--- a/assembly_5/JLCSMT_CPL.xlsx
+++ b/assembly_5/JLCSMT_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\warcgr01\WORKSPACE\moto_logic_board\assembly_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F63E85E-BB26-4310-9DD6-A35B935170AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE54A077-AAD4-46F2-B363-F3D09B271C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
